--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-20.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-20.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -678,12 +678,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -761,12 +761,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -844,12 +844,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -927,12 +927,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-20.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-20.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -678,12 +678,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -761,12 +761,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -844,12 +844,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -927,12 +927,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-20.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-20.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1181,14 +1181,14 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>SEM_PLACAR</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>⚪ SEM_PLACAR</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1593,19 +1593,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S17" t="n">
